--- a/Fuente.xlsx
+++ b/Fuente.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ediazm\Desktop\Eric\2026\2. Codigos\Visor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526A7251-14C2-47FA-84C8-08F6CE5E40C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42172368-3B33-4EBD-9F60-5373B2AABA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CMG-PDO" sheetId="1" r:id="rId1"/>
@@ -15238,13 +15238,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77579099-3DE5-42D9-92B1-5C1A2C42995E}">
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="11.42578125" style="1"/>
@@ -15260,7 +15260,7 @@
       <c r="C1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="14" t="s">
         <v>246</v>
       </c>
     </row>
@@ -15275,7 +15275,7 @@
         <v>249.97</v>
       </c>
       <c r="D2" s="7">
-        <v>263.69719734379191</v>
+        <v>263.69548114193861</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
@@ -15291,7 +15291,7 @@
         <v>248.41</v>
       </c>
       <c r="D3" s="7">
-        <v>261.74020802202358</v>
+        <v>265.11384638969139</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -15307,7 +15307,7 @@
         <v>246.86</v>
       </c>
       <c r="D4" s="7">
-        <v>259.58909219395707</v>
+        <v>264.80894728890308</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -15323,7 +15323,7 @@
         <v>246.86</v>
       </c>
       <c r="D5" s="7">
-        <v>259.36540474892462</v>
+        <v>262.36784042101681</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -15339,7 +15339,7 @@
         <v>246.86</v>
       </c>
       <c r="D6" s="7">
-        <v>258.62622213791258</v>
+        <v>258.75680188479578</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -15355,7 +15355,7 @@
         <v>245.31</v>
       </c>
       <c r="D7" s="7">
-        <v>256.79057909655671</v>
+        <v>253.2590978552175</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -15371,7 +15371,7 @@
         <v>246.86</v>
       </c>
       <c r="D8" s="7">
-        <v>254.58917578177881</v>
+        <v>249.35513237234139</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -15387,7 +15387,7 @@
         <v>246.86</v>
       </c>
       <c r="D9" s="7">
-        <v>252.1453971468425</v>
+        <v>245.7894237378791</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -15403,7 +15403,7 @@
         <v>243.77</v>
       </c>
       <c r="D10" s="7">
-        <v>250.65750097093689</v>
+        <v>246.85693188958501</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
@@ -15419,7 +15419,7 @@
         <v>245.31</v>
       </c>
       <c r="D11" s="7">
-        <v>248.69249602556701</v>
+        <v>248.73074947184591</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -15435,7 +15435,7 @@
         <v>248.41</v>
       </c>
       <c r="D12" s="7">
-        <v>247.14329335309091</v>
+        <v>250.3724074057786</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -15451,7 +15451,7 @@
         <v>245.31</v>
       </c>
       <c r="D13" s="7">
-        <v>245.42569130154811</v>
+        <v>251.55766365595139</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -15467,7 +15467,7 @@
         <v>242.23</v>
       </c>
       <c r="D14" s="7">
-        <v>243.89502984978381</v>
+        <v>249.49278793174841</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -15483,7 +15483,7 @@
         <v>242.23</v>
       </c>
       <c r="D15" s="7">
-        <v>242.726325646627</v>
+        <v>248.56763151090081</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -15499,7 +15499,7 @@
         <v>240.7</v>
       </c>
       <c r="D16" s="7">
-        <v>240.8995857616483</v>
+        <v>245.99947891267641</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -15515,7 +15515,7 @@
         <v>239.18</v>
       </c>
       <c r="D17" s="7">
-        <v>241.23718833099551</v>
+        <v>245.04412448771919</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -15531,7 +15531,7 @@
         <v>237.66</v>
       </c>
       <c r="D18" s="7">
-        <v>241.86736784660809</v>
+        <v>245.3841119966751</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -15547,7 +15547,7 @@
         <v>240.7</v>
       </c>
       <c r="D19" s="7">
-        <v>242.6930165305026</v>
+        <v>246.06087867425799</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -15563,7 +15563,7 @@
         <v>246.86</v>
       </c>
       <c r="D20" s="7">
-        <v>243.86126232785961</v>
+        <v>246.13180056396189</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -15579,7 +15579,7 @@
         <v>246.86</v>
       </c>
       <c r="D21" s="7">
-        <v>242.8373578699956</v>
+        <v>245.68806089037861</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -15595,7 +15595,7 @@
         <v>242.23</v>
       </c>
       <c r="D22" s="7">
-        <v>241.62596314224211</v>
+        <v>244.99696604767931</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -15611,7 +15611,7 @@
         <v>236.15</v>
       </c>
       <c r="D23" s="7">
-        <v>239.5372662228437</v>
+        <v>241.81403419366541</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -15627,7 +15627,7 @@
         <v>231.64</v>
       </c>
       <c r="D24" s="7">
-        <v>238.48992029270369</v>
+        <v>239.28383638901869</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -15643,7 +15643,7 @@
         <v>230.15</v>
       </c>
       <c r="D25" s="7">
-        <v>237.0984066807487</v>
+        <v>239.84656435884281</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -15661,7 +15661,7 @@
         <v>230.15</v>
       </c>
       <c r="D26" s="7">
-        <v>235.856804128915</v>
+        <v>240.96847556531651</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -15679,7 +15679,7 @@
         <v>230.15</v>
       </c>
       <c r="D27" s="7">
-        <v>235.3197116288207</v>
+        <v>241.0738899446921</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -15697,7 +15697,7 @@
         <v>228.67</v>
       </c>
       <c r="D28" s="7">
-        <v>234.80155214347729</v>
+        <v>239.57956695419711</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -15715,7 +15715,7 @@
         <v>225.71</v>
       </c>
       <c r="D29" s="7">
-        <v>233.8685390494887</v>
+        <v>237.1414911185978</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -15733,7 +15733,7 @@
         <v>221.33</v>
       </c>
       <c r="D30" s="7">
-        <v>231.40481294680669</v>
+        <v>232.43368044969509</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -15751,7 +15751,7 @@
         <v>219.88</v>
       </c>
       <c r="D31" s="7">
-        <v>228.76149441304531</v>
+        <v>227.13489922616759</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -15769,7 +15769,7 @@
         <v>216.99</v>
       </c>
       <c r="D32" s="7">
-        <v>227.36315727023279</v>
+        <v>224.1623257385678</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -15787,7 +15787,7 @@
         <v>216.99</v>
       </c>
       <c r="D33" s="7">
-        <v>225.8190893808393</v>
+        <v>222.9009932695482</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -15805,7 +15805,7 @@
         <v>216.99</v>
       </c>
       <c r="D34" s="7">
-        <v>224.1889776118135</v>
+        <v>223.90219533459651</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -15823,7 +15823,7 @@
         <v>218.43</v>
       </c>
       <c r="D35" s="7">
-        <v>222.87809623152839</v>
+        <v>223.9329938305745</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -15841,7 +15841,7 @@
         <v>219.88</v>
       </c>
       <c r="D36" s="7">
-        <v>222.51601614947251</v>
+        <v>221.98631284947791</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -15859,7 +15859,7 @@
         <v>216.99</v>
       </c>
       <c r="D37" s="7">
-        <v>220.326412784729</v>
+        <v>220.0882787696965</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -15877,7 +15877,7 @@
         <v>211.29</v>
       </c>
       <c r="D38" s="7">
-        <v>216.72462558214571</v>
+        <v>217.51418392193219</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -15895,7 +15895,7 @@
         <v>205.67</v>
       </c>
       <c r="D39" s="7">
-        <v>214.42397966300931</v>
+        <v>215.0847907811511</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -15913,7 +15913,7 @@
         <v>202.9</v>
       </c>
       <c r="D40" s="7">
-        <v>213.04478367854981</v>
+        <v>212.48256840888681</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -15931,7 +15931,7 @@
         <v>204.28</v>
       </c>
       <c r="D41" s="7">
-        <v>213.05932126457719</v>
+        <v>213.65596549627011</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
@@ -15949,7 +15949,7 @@
         <v>207.07</v>
       </c>
       <c r="D42" s="7">
-        <v>212.8625954676013</v>
+        <v>214.30898382317531</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -15967,7 +15967,7 @@
         <v>205.67</v>
       </c>
       <c r="D43" s="7">
-        <v>212.37559071934999</v>
+        <v>212.66321826171759</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -15985,7 +15985,7 @@
         <v>202.9</v>
       </c>
       <c r="D44" s="7">
-        <v>211.3612235523656</v>
+        <v>210.5622085243194</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -16003,7 +16003,7 @@
         <v>201.52</v>
       </c>
       <c r="D45" s="7">
-        <v>210.01553554096569</v>
+        <v>206.42386222939541</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -16021,7 +16021,7 @@
         <v>201.52</v>
       </c>
       <c r="D46" s="7">
-        <v>208.73002308506921</v>
+        <v>203.1434007190955</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -16039,7 +16039,7 @@
         <v>202.9</v>
       </c>
       <c r="D47" s="7">
-        <v>207.09310979921341</v>
+        <v>202.5027806081545</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -16057,7 +16057,7 @@
         <v>204.28</v>
       </c>
       <c r="D48" s="7">
-        <v>207.08147351707279</v>
+        <v>205.39950225857211</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -16075,7 +16075,7 @@
         <v>202.9</v>
       </c>
       <c r="D49" s="7">
-        <v>206.94564435629999</v>
+        <v>207.01581677947641</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -16093,7 +16093,7 @@
         <v>200.15</v>
       </c>
       <c r="D50" s="7">
-        <v>206.76312590306921</v>
+        <v>206.65428746961271</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -16109,7 +16109,7 @@
         <v>202.9</v>
       </c>
       <c r="D51" s="7">
-        <v>207.16236740749531</v>
+        <v>205.25975741910699</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -16125,7 +16125,7 @@
         <v>204.28</v>
       </c>
       <c r="D52" s="7">
-        <v>206.6418936211829</v>
+        <v>204.04007773835281</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -16141,7 +16141,7 @@
         <v>205.67</v>
       </c>
       <c r="D53" s="7">
-        <v>205.93206511983951</v>
+        <v>204.06901707267471</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -16157,7 +16157,7 @@
         <v>207.07</v>
       </c>
       <c r="D54" s="7">
-        <v>205.46497629144849</v>
+        <v>205.9643967942859</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -16173,7 +16173,7 @@
         <v>207.07</v>
       </c>
       <c r="D55" s="7">
-        <v>206.9037547117791</v>
+        <v>207.11501415256421</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -16189,7 +16189,7 @@
         <v>207.07</v>
       </c>
       <c r="D56" s="7">
-        <v>208.44572851305921</v>
+        <v>206.42410265840269</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -16205,7 +16205,7 @@
         <v>208.47</v>
       </c>
       <c r="D57" s="7">
-        <v>209.09127535698121</v>
+        <v>207.26017187853151</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -16221,7 +16221,7 @@
         <v>211.29</v>
       </c>
       <c r="D58" s="7">
-        <v>209.1855118333269</v>
+        <v>208.44581689496829</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -16237,7 +16237,7 @@
         <v>212.71</v>
       </c>
       <c r="D59" s="7">
-        <v>209.61374614518411</v>
+        <v>209.80441659429039</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -16253,7 +16253,7 @@
         <v>219.88</v>
       </c>
       <c r="D60" s="7">
-        <v>210.05872091697771</v>
+        <v>211.61487622742331</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -16269,7 +16269,7 @@
         <v>221.33</v>
       </c>
       <c r="D61" s="7">
-        <v>212.16863370561049</v>
+        <v>214.12783745469619</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -16285,7 +16285,7 @@
         <v>219.88</v>
       </c>
       <c r="D62" s="7">
-        <v>213.5131101366662</v>
+        <v>214.9944596596203</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -16301,7 +16301,7 @@
         <v>218.43</v>
       </c>
       <c r="D63" s="7">
-        <v>214.07569022404141</v>
+        <v>217.65334987233791</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -16317,7 +16317,7 @@
         <v>215.56</v>
       </c>
       <c r="D64" s="7">
-        <v>214.65889008208251</v>
+        <v>219.98113567845041</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -16333,7 +16333,7 @@
         <v>214.13</v>
       </c>
       <c r="D65" s="7">
-        <v>215.10322980893281</v>
+        <v>221.10512879016571</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -16349,7 +16349,7 @@
         <v>211.29</v>
       </c>
       <c r="D66" s="7">
-        <v>215.2723898303739</v>
+        <v>222.9339934818544</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -16365,7 +16365,7 @@
         <v>211.29</v>
       </c>
       <c r="D67" s="7">
-        <v>216.58744886271859</v>
+        <v>220.79241866176969</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -16381,7 +16381,7 @@
         <v>211.29</v>
       </c>
       <c r="D68" s="7">
-        <v>217.74872637514019</v>
+        <v>219.3449916827575</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -16397,7 +16397,7 @@
         <v>215.56</v>
       </c>
       <c r="D69" s="7">
-        <v>217.42112489560199</v>
+        <v>216.55959148232381</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -16413,7 +16413,7 @@
         <v>216.99</v>
       </c>
       <c r="D70" s="7">
-        <v>217.39010707706339</v>
+        <v>213.9740966495518</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -16429,7 +16429,7 @@
         <v>216.99</v>
       </c>
       <c r="D71" s="7">
-        <v>217.4330405315954</v>
+        <v>210.83616873060799</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -16445,7 +16445,7 @@
         <v>225.71</v>
       </c>
       <c r="D72" s="7">
-        <v>216.423267173368</v>
+        <v>211.08901399408421</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -16461,7 +16461,7 @@
         <v>225.71</v>
       </c>
       <c r="D73" s="7">
-        <v>216.0066556447922</v>
+        <v>213.57943449515449</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -16477,7 +16477,7 @@
         <v>224.25</v>
       </c>
       <c r="D74" s="7">
-        <v>213.96757662605651</v>
+        <v>217.38642812207041</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -16493,7 +16493,7 @@
         <v>227.19</v>
       </c>
       <c r="D75" s="7">
-        <v>214.5370680875094</v>
+        <v>222.73758669232359</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -16509,7 +16509,7 @@
         <v>228.67</v>
       </c>
       <c r="D76" s="7">
-        <v>215.23359468490989</v>
+        <v>226.90622689293599</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -16525,7 +16525,7 @@
         <v>227.19</v>
       </c>
       <c r="D77" s="7">
-        <v>217.59013543552959</v>
+        <v>228.61166295846161</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -16541,7 +16541,7 @@
         <v>227.19</v>
       </c>
       <c r="D78" s="7">
-        <v>219.46283456879769</v>
+        <v>229.42419799784059</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -16557,7 +16557,7 @@
         <v>231.64</v>
       </c>
       <c r="D79" s="7">
-        <v>222.71248445419869</v>
+        <v>230.9338009799155</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -16573,7 +16573,7 @@
         <v>237.66</v>
       </c>
       <c r="D80" s="7">
-        <v>226.8692378241482</v>
+        <v>231.12524192234019</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -16589,7 +16589,7 @@
         <v>237.66</v>
       </c>
       <c r="D81" s="7">
-        <v>231.08967127642561</v>
+        <v>232.1508606980056</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -16605,7 +16605,7 @@
         <v>236.15</v>
       </c>
       <c r="D82" s="7">
-        <v>234.02716808318971</v>
+        <v>236.81483289322361</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -16621,7 +16621,7 @@
         <v>236.15</v>
       </c>
       <c r="D83" s="7">
-        <v>235.08925278024859</v>
+        <v>237.13836958092591</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -16637,7 +16637,7 @@
         <v>242.23</v>
       </c>
       <c r="D84" s="7">
-        <v>236.4996408069691</v>
+        <v>236.1341381619462</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -16653,7 +16653,7 @@
         <v>253.1</v>
       </c>
       <c r="D85" s="7">
-        <v>235.33407646658239</v>
+        <v>238.66179984381591</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -16665,8 +16665,11 @@
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
+      <c r="C86" s="5">
+        <v>261.04000000000002</v>
+      </c>
       <c r="D86" s="7">
-        <v>233.6909991396756</v>
+        <v>243.90836946733711</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -16678,8 +16681,11 @@
         <f t="shared" si="1"/>
         <v>0.54166666666666696</v>
       </c>
+      <c r="C87" s="5">
+        <v>264.25</v>
+      </c>
       <c r="D87" s="7">
-        <v>233.65124383115119</v>
+        <v>247.17899764677321</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -16691,8 +16697,11 @@
         <f t="shared" si="1"/>
         <v>0.58333333333333304</v>
       </c>
+      <c r="C88" s="5">
+        <v>270.75</v>
+      </c>
       <c r="D88" s="7">
-        <v>234.21888610085949</v>
+        <v>252.19289406355401</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -16704,8 +16713,11 @@
         <f t="shared" si="1"/>
         <v>0.625</v>
       </c>
+      <c r="C89" s="5">
+        <v>280.67</v>
+      </c>
       <c r="D89" s="7">
-        <v>233.15421533527049</v>
+        <v>259.19605691813553</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -16717,21 +16729,27 @@
         <f t="shared" si="1"/>
         <v>0.66666666666666696</v>
       </c>
+      <c r="C90" s="5">
+        <v>289.10000000000002</v>
+      </c>
       <c r="D90" s="7">
-        <v>231.90526654451699</v>
+        <v>266.00366330722892</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <f t="shared" ref="A91:A112" si="2">+A67+1</f>
+        <f t="shared" ref="A91:A154" si="2">+A67+1</f>
         <v>46052</v>
       </c>
       <c r="B91" s="3">
-        <f t="shared" ref="B91:B112" si="3">+B67</f>
+        <f t="shared" ref="B91:B154" si="3">+B67</f>
         <v>0.70833333333333304</v>
       </c>
+      <c r="C91" s="5">
+        <v>297.68</v>
+      </c>
       <c r="D91" s="7">
-        <v>230.8702930708755</v>
+        <v>274.91052316531801</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -16743,8 +16761,11 @@
         <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
+      <c r="C92" s="5">
+        <v>306.39999999999998</v>
+      </c>
       <c r="D92" s="7">
-        <v>231.74996455186201</v>
+        <v>285.05320249707398</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -16756,8 +16777,11 @@
         <f t="shared" si="3"/>
         <v>0.79166666666666696</v>
       </c>
+      <c r="C93" s="5">
+        <v>317.06</v>
+      </c>
       <c r="D93" s="7">
-        <v>234.8204317763165</v>
+        <v>293.59983813713399</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -16769,8 +16793,11 @@
         <f t="shared" si="3"/>
         <v>0.83333333333333304</v>
       </c>
+      <c r="C94" s="5">
+        <v>322.48</v>
+      </c>
       <c r="D94" s="7">
-        <v>236.45938433425579</v>
+        <v>299.38310382887232</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -16782,8 +16809,11 @@
         <f t="shared" si="3"/>
         <v>0.875</v>
       </c>
+      <c r="C95" s="5">
+        <v>318.86</v>
+      </c>
       <c r="D95" s="7">
-        <v>235.78699075007569</v>
+        <v>303.73341720288141</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -16795,8 +16825,11 @@
         <f t="shared" si="3"/>
         <v>0.91666666666666696</v>
       </c>
+      <c r="C96" s="5">
+        <v>309.93</v>
+      </c>
       <c r="D96" s="7">
-        <v>235.6900674898433</v>
+        <v>305.98111499957849</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -16808,8 +16841,11 @@
         <f t="shared" si="3"/>
         <v>0.95833333333333304</v>
       </c>
+      <c r="C97" s="5">
+        <v>302.89</v>
+      </c>
       <c r="D97" s="7">
-        <v>235.35245141222109</v>
+        <v>307.99809191458132</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -16821,8 +16857,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="C98" s="5">
+        <v>301.14999999999998</v>
+      </c>
       <c r="D98" s="7">
-        <v>234.40310861373521</v>
+        <v>311.89063258111258</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -16834,8 +16873,11 @@
         <f t="shared" si="3"/>
         <v>4.1666666666666664E-2</v>
       </c>
+      <c r="C99" s="5">
+        <v>299.41000000000003</v>
+      </c>
       <c r="D99" s="7">
-        <v>232.87334229123451</v>
+        <v>314.35427963068219</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -16847,8 +16889,11 @@
         <f t="shared" si="3"/>
         <v>8.3333333333333301E-2</v>
       </c>
+      <c r="C100" s="5">
+        <v>297.67</v>
+      </c>
       <c r="D100" s="7">
-        <v>231.73764417518819</v>
+        <v>314.68292562474687</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -16860,8 +16905,11 @@
         <f t="shared" si="3"/>
         <v>0.125</v>
       </c>
+      <c r="C101" s="5">
+        <v>301.14999999999998</v>
+      </c>
       <c r="D101" s="7">
-        <v>231.75889580372811</v>
+        <v>314.17117709377328</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
@@ -16873,8 +16921,11 @@
         <f t="shared" si="3"/>
         <v>0.16666666666666699</v>
       </c>
+      <c r="C102" s="5">
+        <v>301.14999999999998</v>
+      </c>
       <c r="D102" s="7">
-        <v>233.74410298846371</v>
+        <v>310.94456794861208</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
@@ -16886,8 +16937,11 @@
         <f t="shared" si="3"/>
         <v>0.20833333333333301</v>
       </c>
+      <c r="C103" s="5">
+        <v>301.14999999999998</v>
+      </c>
       <c r="D103" s="7">
-        <v>234.31282645076291</v>
+        <v>306.87504419231578</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
@@ -16899,8 +16953,11 @@
         <f t="shared" si="3"/>
         <v>0.25</v>
       </c>
+      <c r="C104" s="5">
+        <v>301.14999999999998</v>
+      </c>
       <c r="D104" s="7">
-        <v>232.8702312762228</v>
+        <v>303.73219821219442</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
@@ -16912,8 +16969,11 @@
         <f t="shared" si="3"/>
         <v>0.29166666666666702</v>
       </c>
+      <c r="C105" s="5">
+        <v>318.86</v>
+      </c>
       <c r="D105" s="7">
-        <v>231.5153530964223</v>
+        <v>304.99294865564173</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
@@ -16925,8 +16985,11 @@
         <f t="shared" si="3"/>
         <v>0.33333333333333298</v>
       </c>
+      <c r="C106" s="5">
+        <v>333.46</v>
+      </c>
       <c r="D106" s="7">
-        <v>230.99844580603511</v>
+        <v>309.6397772988359</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
@@ -16938,8 +17001,11 @@
         <f t="shared" si="3"/>
         <v>0.375</v>
       </c>
+      <c r="C107" s="5">
+        <v>342.78</v>
+      </c>
       <c r="D107" s="7">
-        <v>231.35751286693059</v>
+        <v>318.61389502108511</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -16951,8 +17017,11 @@
         <f t="shared" si="3"/>
         <v>0.41666666666666702</v>
       </c>
+      <c r="C108" s="5">
+        <v>348.45</v>
+      </c>
       <c r="D108" s="7">
-        <v>231.3430018007073</v>
+        <v>327.18810608582919</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
@@ -16964,8 +17033,11 @@
         <f t="shared" si="3"/>
         <v>0.45833333333333298</v>
       </c>
+      <c r="C109" s="5">
+        <v>342.78</v>
+      </c>
       <c r="D109" s="7">
-        <v>232.54086595983449</v>
+        <v>331.51315357494292</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -16977,8 +17049,11 @@
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
+      <c r="C110" s="5">
+        <v>329.78</v>
+      </c>
       <c r="D110" s="7">
-        <v>233.78861943533281</v>
+        <v>333.31245076601869</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -16990,8 +17065,11 @@
         <f t="shared" si="3"/>
         <v>0.54166666666666696</v>
       </c>
+      <c r="C111" s="5">
+        <v>322.48</v>
+      </c>
       <c r="D111" s="7">
-        <v>234.18405253026901</v>
+        <v>334.26998177490992</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
@@ -17003,9 +17081,1078 @@
         <f t="shared" si="3"/>
         <v>0.58333333333333304</v>
       </c>
+      <c r="C112" s="5">
+        <v>322.48</v>
+      </c>
       <c r="D112" s="7">
-        <v>234.10853440286141</v>
-      </c>
+        <v>337.54443219993829</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B113" s="3">
+        <f t="shared" si="3"/>
+        <v>0.625</v>
+      </c>
+      <c r="C113" s="5">
+        <v>322.48</v>
+      </c>
+      <c r="D113" s="7">
+        <v>338.444390889499</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B114" s="3">
+        <f t="shared" si="3"/>
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="C114" s="5">
+        <v>324.29000000000002</v>
+      </c>
+      <c r="D114" s="7">
+        <v>338.18671011202599</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B115" s="3">
+        <f t="shared" si="3"/>
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="C115" s="5">
+        <v>329.78</v>
+      </c>
+      <c r="D115" s="7">
+        <v>337.42319743819519</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B116" s="3">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="C116" s="5">
+        <v>379.04</v>
+      </c>
+      <c r="D116" s="7">
+        <v>340.428014816325</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B117" s="3">
+        <f t="shared" si="3"/>
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="C117" s="5">
+        <v>340.91</v>
+      </c>
+      <c r="D117" s="7">
+        <v>337.66567382660639</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B118" s="3">
+        <f t="shared" si="3"/>
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="C118" s="5">
+        <v>342.78</v>
+      </c>
+      <c r="D118" s="7">
+        <v>337.30555862487341</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B119" s="3">
+        <f t="shared" si="3"/>
+        <v>0.875</v>
+      </c>
+      <c r="C119" s="5">
+        <v>344.67</v>
+      </c>
+      <c r="D119" s="7">
+        <v>341.85857477179258</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B120" s="3">
+        <f t="shared" si="3"/>
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="C120" s="5">
+        <v>342.78</v>
+      </c>
+      <c r="D120" s="7">
+        <v>345.76887613400061</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <f t="shared" si="2"/>
+        <v>46053</v>
+      </c>
+      <c r="B121" s="3">
+        <f t="shared" si="3"/>
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="C121" s="5">
+        <v>337.17</v>
+      </c>
+      <c r="D121" s="7">
+        <v>347.9101130491095</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B122" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C122" s="5">
+        <v>340.91</v>
+      </c>
+      <c r="D122" s="7">
+        <v>351.77742592661662</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B123" s="3">
+        <f t="shared" si="3"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C123" s="5">
+        <v>363.75</v>
+      </c>
+      <c r="D123" s="7">
+        <v>356.44883123378412</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B124" s="3">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333301E-2</v>
+      </c>
+      <c r="C124" s="5">
+        <v>395.75</v>
+      </c>
+      <c r="D124" s="7">
+        <v>355.95471711539261</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B125" s="3">
+        <f t="shared" si="3"/>
+        <v>0.125</v>
+      </c>
+      <c r="C125" s="5">
+        <v>433.56</v>
+      </c>
+      <c r="D125" s="7">
+        <v>368.73933455501412</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B126" s="3">
+        <f t="shared" si="3"/>
+        <v>0.16666666666666699</v>
+      </c>
+      <c r="C126" s="5">
+        <v>433.56</v>
+      </c>
+      <c r="D126" s="7">
+        <v>381.86988286071619</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B127" s="3">
+        <f t="shared" si="3"/>
+        <v>0.20833333333333301</v>
+      </c>
+      <c r="C127" s="5">
+        <v>431.41</v>
+      </c>
+      <c r="D127" s="7">
+        <v>392.51275853508167</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B128" s="3">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="C128" s="5">
+        <v>448.81</v>
+      </c>
+      <c r="D128" s="7">
+        <v>404.74159335135761</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B129" s="3">
+        <f t="shared" si="3"/>
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="C129" s="5">
+        <v>471.14</v>
+      </c>
+      <c r="D129" s="7">
+        <v>421.88695090592722</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B130" s="3">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="C130" s="5">
+        <v>496.45</v>
+      </c>
+      <c r="D130" s="7">
+        <v>441.6449851215956</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B131" s="3">
+        <f t="shared" si="3"/>
+        <v>0.375</v>
+      </c>
+      <c r="C131" s="5">
+        <v>505.84</v>
+      </c>
+      <c r="D131" s="7">
+        <v>458.85198758099341</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B132" s="3">
+        <f t="shared" si="3"/>
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="C132" s="5">
+        <v>512.95000000000005</v>
+      </c>
+      <c r="D132" s="7">
+        <v>476.55917079290771</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B133" s="3">
+        <f t="shared" si="3"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="C133" s="5">
+        <v>524.94000000000005</v>
+      </c>
+      <c r="D133" s="7">
+        <v>489.699088371882</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B134" s="3">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="C134" s="5">
+        <v>539.54</v>
+      </c>
+      <c r="D134" s="7">
+        <v>503.7364728599847</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B135" s="3">
+        <f t="shared" si="3"/>
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="C135" s="5">
+        <v>551.88</v>
+      </c>
+      <c r="D135" s="7">
+        <v>517.77994705247056</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B136" s="3">
+        <f t="shared" si="3"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="C136" s="5">
+        <v>569.44000000000005</v>
+      </c>
+      <c r="D136" s="7">
+        <v>532.69627675833124</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B137" s="3">
+        <f t="shared" si="3"/>
+        <v>0.625</v>
+      </c>
+      <c r="C137" s="5">
+        <v>587.32000000000005</v>
+      </c>
+      <c r="D137" s="7">
+        <v>547.40597603541266</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B138" s="3">
+        <f t="shared" si="3"/>
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="C138" s="5">
+        <v>600.29999999999995</v>
+      </c>
+      <c r="D138" s="7">
+        <v>563.10091806290814</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B139" s="3">
+        <f t="shared" si="3"/>
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="C139" s="5">
+        <v>602.91</v>
+      </c>
+      <c r="D139" s="7">
+        <v>575.68754206218341</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B140" s="3">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="C140" s="5">
+        <v>597.69000000000005</v>
+      </c>
+      <c r="D140" s="7">
+        <v>583.96232282080484</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B141" s="3">
+        <f t="shared" si="3"/>
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="C141" s="5">
+        <v>589.9</v>
+      </c>
+      <c r="D141" s="7">
+        <v>591.41648334898798</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B142" s="3">
+        <f t="shared" si="3"/>
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="C142" s="5">
+        <v>577.07000000000005</v>
+      </c>
+      <c r="D142" s="7">
+        <v>596.52844719359518</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B143" s="3">
+        <f t="shared" si="3"/>
+        <v>0.875</v>
+      </c>
+      <c r="C143" s="5">
+        <v>564.39</v>
+      </c>
+      <c r="D143" s="7">
+        <v>598.4407283758087</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B144" s="3">
+        <f t="shared" si="3"/>
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="C144" s="5">
+        <v>559.37</v>
+      </c>
+      <c r="D144" s="7">
+        <v>599.06833432751739</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" s="2">
+        <f t="shared" si="2"/>
+        <v>46054</v>
+      </c>
+      <c r="B145" s="3">
+        <f t="shared" si="3"/>
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="C145" s="5">
+        <v>569.44000000000005</v>
+      </c>
+      <c r="D145" s="7">
+        <v>598.54412848035679</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B146" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="C146" s="5">
+        <v>595.09</v>
+      </c>
+      <c r="D146" s="7">
+        <v>596.81900643524864</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B147" s="3">
+        <f t="shared" si="3"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C147" s="5">
+        <v>626.74</v>
+      </c>
+      <c r="D147" s="7">
+        <v>598.78730062856994</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B148" s="3">
+        <f t="shared" si="3"/>
+        <v>8.3333333333333301E-2</v>
+      </c>
+      <c r="C148" s="5">
+        <v>664.89</v>
+      </c>
+      <c r="D148" s="7">
+        <v>607.4965919874287</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B149" s="3">
+        <f t="shared" si="3"/>
+        <v>0.125</v>
+      </c>
+      <c r="C149" s="5">
+        <v>673.24</v>
+      </c>
+      <c r="D149" s="7">
+        <v>619.2237433121561</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B150" s="3">
+        <f t="shared" si="3"/>
+        <v>0.16666666666666699</v>
+      </c>
+      <c r="C150" s="5">
+        <v>670.45</v>
+      </c>
+      <c r="D150" s="7">
+        <v>628.19919653477154</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B151" s="3">
+        <f t="shared" si="3"/>
+        <v>0.20833333333333301</v>
+      </c>
+      <c r="C151" s="5">
+        <v>659.36</v>
+      </c>
+      <c r="D151" s="7">
+        <v>639.85785542665485</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B152" s="3">
+        <f t="shared" si="3"/>
+        <v>0.25</v>
+      </c>
+      <c r="C152" s="5">
+        <v>651.11</v>
+      </c>
+      <c r="D152" s="7">
+        <v>648.94043877176045</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B153" s="3">
+        <f t="shared" si="3"/>
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="C153" s="5">
+        <v>659.36</v>
+      </c>
+      <c r="D153" s="7">
+        <v>659.46941471996593</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <f t="shared" si="2"/>
+        <v>46055</v>
+      </c>
+      <c r="B154" s="3">
+        <f t="shared" si="3"/>
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="C154" s="5">
+        <v>676.04</v>
+      </c>
+      <c r="D154" s="7">
+        <v>671.20235421249356</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" s="2">
+        <f t="shared" ref="A155:A191" si="4">+A131+1</f>
+        <v>46055</v>
+      </c>
+      <c r="B155" s="3">
+        <f t="shared" ref="B155:B191" si="5">+B131</f>
+        <v>0.375</v>
+      </c>
+      <c r="C155" s="5">
+        <v>687.29</v>
+      </c>
+      <c r="D155" s="7">
+        <v>679.42472195906976</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B156" s="3">
+        <f t="shared" si="5"/>
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D156" s="7">
+        <v>681.69410115112851</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B157" s="3">
+        <f t="shared" si="5"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D157" s="7">
+        <v>685.21279051855322</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B158" s="3">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="D158" s="7">
+        <v>688.16255301834713</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B159" s="3">
+        <f t="shared" si="5"/>
+        <v>0.54166666666666696</v>
+      </c>
+      <c r="D159" s="7">
+        <v>687.02782895859787</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B160" s="3">
+        <f t="shared" si="5"/>
+        <v>0.58333333333333304</v>
+      </c>
+      <c r="D160" s="7">
+        <v>683.67923499620292</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B161" s="3">
+        <f t="shared" si="5"/>
+        <v>0.625</v>
+      </c>
+      <c r="D161" s="7">
+        <v>680.00208625492473</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B162" s="3">
+        <f t="shared" si="5"/>
+        <v>0.66666666666666696</v>
+      </c>
+      <c r="D162" s="7">
+        <v>678.34694796610222</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B163" s="3">
+        <f t="shared" si="5"/>
+        <v>0.70833333333333304</v>
+      </c>
+      <c r="D163" s="7">
+        <v>677.50700871589095</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B164" s="3">
+        <f t="shared" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="D164" s="7">
+        <v>677.43604185034792</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B165" s="3">
+        <f t="shared" si="5"/>
+        <v>0.79166666666666696</v>
+      </c>
+      <c r="D165" s="7">
+        <v>676.39863660271635</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B166" s="3">
+        <f t="shared" si="5"/>
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="D166" s="7">
+        <v>674.13799538644412</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B167" s="3">
+        <f t="shared" si="5"/>
+        <v>0.875</v>
+      </c>
+      <c r="D167" s="7">
+        <v>670.2709515648861</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B168" s="3">
+        <f t="shared" si="5"/>
+        <v>0.91666666666666696</v>
+      </c>
+      <c r="D168" s="7">
+        <v>666.89092702700066</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <f t="shared" si="4"/>
+        <v>46055</v>
+      </c>
+      <c r="B169" s="3">
+        <f t="shared" si="5"/>
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="D169" s="7">
+        <v>665.06957988524732</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B170" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="D170" s="7">
+        <v>663.87393506187368</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B171" s="3">
+        <f t="shared" si="5"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D171" s="7">
+        <v>660.52621409188282</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B172" s="3">
+        <f t="shared" si="5"/>
+        <v>8.3333333333333301E-2</v>
+      </c>
+      <c r="D172" s="7">
+        <v>654.88218785000902</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B173" s="3">
+        <f t="shared" si="5"/>
+        <v>0.125</v>
+      </c>
+      <c r="D173" s="7">
+        <v>651.92972461223917</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B174" s="3">
+        <f t="shared" si="5"/>
+        <v>0.16666666666666699</v>
+      </c>
+      <c r="D174" s="7">
+        <v>652.3465763282361</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B175" s="3">
+        <f t="shared" si="5"/>
+        <v>0.20833333333333301</v>
+      </c>
+      <c r="D175" s="7">
+        <v>654.96169107470257</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B176" s="3">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="D176" s="7">
+        <v>661.56241053880126</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B177" s="3">
+        <f t="shared" si="5"/>
+        <v>0.29166666666666702</v>
+      </c>
+      <c r="D177" s="7">
+        <v>670.61275518731463</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B178" s="3">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="D178" s="7">
+        <v>679.0981179644898</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B179" s="3">
+        <f t="shared" si="5"/>
+        <v>0.375</v>
+      </c>
+      <c r="D179" s="7">
+        <v>686.0119906473625</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B180" s="3">
+        <f t="shared" si="5"/>
+        <v>0.41666666666666702</v>
+      </c>
+      <c r="D180" s="7">
+        <v>695.39356875150725</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" s="2">
+        <f t="shared" si="4"/>
+        <v>46056</v>
+      </c>
+      <c r="B181" s="3">
+        <f t="shared" si="5"/>
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D181" s="7">
+        <v>706.21470083539657</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" s="2"/>
+      <c r="B182" s="3"/>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" s="2"/>
+      <c r="B183" s="3"/>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" s="2"/>
+      <c r="B184" s="3"/>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" s="2"/>
+      <c r="B185" s="3"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" s="2"/>
+      <c r="B186" s="3"/>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" s="2"/>
+      <c r="B187" s="3"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" s="2"/>
+      <c r="B188" s="3"/>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" s="2"/>
+      <c r="B189" s="3"/>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" s="2"/>
+      <c r="B190" s="3"/>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" s="2"/>
+      <c r="B191" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
